--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:49:35+00:00</t>
+    <t>2026-01-30T11:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T11:01:37+00:00</t>
+    <t>2026-01-30T14:32:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Date d’admission</t>
+    <t>TDDUI Admission Date</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:32:15+00:00</t>
+    <t>2026-02-09T09:12:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T09:12:46+00:00</t>
+    <t>2026-02-10T10:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:23:53+00:00</t>
+    <t>2026-02-11T15:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:25:25+00:00</t>
+    <t>2026-02-16T10:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:19:26+00:00</t>
+    <t>2026-02-23T14:19:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T14:19:51+00:00</t>
+    <t>2026-02-24T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-admission-date.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:04:30+00:00</t>
+    <t>2026-02-26T15:31:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
